--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
@@ -776,7 +776,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>138.6238172098828</v>
+        <v>138.6238172098829</v>
       </c>
       <c r="C25">
         <v>143.2984274755447</v>
@@ -793,7 +793,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.9762240648583298</v>
+        <v>0.97622406485833</v>
       </c>
       <c r="C26">
         <v>0.981496078599621</v>
@@ -5298,7 +5298,7 @@
         <v>290</v>
       </c>
       <c r="B291">
-        <v>230.5666422499899</v>
+        <v>230.56664224999</v>
       </c>
       <c r="C291">
         <v>254.6353465819536</v>
